--- a/基金/持仓基金/270023_广发全球精选股票_QDII_人民币A/270023_交易记录.xlsx
+++ b/基金/持仓基金/270023_广发全球精选股票_QDII_人民币A/270023_交易记录.xlsx
@@ -3180,7 +3180,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" sqref="D2:D130">
-      <formula1>"买入,卖出"</formula1>
+      <formula1>"买入,卖出,转入"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
